--- a/Баг_Репорты ДЗ №2.xlsx
+++ b/Баг_Репорты ДЗ №2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivankosarev/Documents/ВУЗ/Программная инженерия/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AF004E1-488B-554F-B3B2-263879517A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7108E28E-99F7-7B42-A4DD-47A1B80FAC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17140" xr2:uid="{2F60AE98-D34A-7F44-8ACA-8D360F42C4F9}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
   <si>
     <t>№ бага</t>
   </si>
   <si>
-    <t>ID багрепорта</t>
-  </si>
-  <si>
     <t>Заголовок</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
     <t>iOS 27.0.1</t>
   </si>
   <si>
-    <t>Серьезность -/5</t>
-  </si>
-  <si>
     <t>Ссылка</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
     <t>iPadOS 27.0.1</t>
   </si>
   <si>
-    <t>Некорректное отображение геолокации</t>
-  </si>
-  <si>
     <t>Использование "Яндекс Карты" в адмиралтейском районе</t>
   </si>
   <si>
@@ -182,9 +173,6 @@
     <t>Версия 9.1.3(1) iPadOS 27.0.1</t>
   </si>
   <si>
-    <t>Невозможность переноса виджета на соседнюю страницу</t>
-  </si>
-  <si>
     <t>1. Добавить виджет приложения "Мой Дом" 2. Перенести виджет на соседнюю страницу</t>
   </si>
   <si>
@@ -279,6 +267,30 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1TpAEKeQVBb6OJ4WaUIBX5U2z9D3rJBM_/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Серьезность</t>
+  </si>
+  <si>
+    <t>Незначительный</t>
+  </si>
+  <si>
+    <t>Значителный</t>
+  </si>
+  <si>
+    <t>Критический</t>
+  </si>
+  <si>
+    <t>Блокирующий</t>
+  </si>
+  <si>
+    <t>ID баг-репорта</t>
+  </si>
+  <si>
+    <t>Некорректное отображение геолокации в центре СПб</t>
+  </si>
+  <si>
+    <t>Невозможность переноса виджета "Мой Дом" на соседнюю страницу рабочего стола в iPadOS</t>
   </si>
 </sst>
 </file>
@@ -698,7 +710,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="12.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" style="1" customWidth="1"/>
@@ -710,39 +722,39 @@
     <col min="11" max="11" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="71" customHeight="1" x14ac:dyDescent="0.2">
@@ -750,34 +762,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="1">
-        <v>2</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -785,31 +797,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="1">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="136" x14ac:dyDescent="0.2">
@@ -817,31 +829,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="1">
-        <v>3</v>
+      <c r="I4" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="136" x14ac:dyDescent="0.2">
@@ -849,31 +861,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="1">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="85" x14ac:dyDescent="0.2">
@@ -881,31 +893,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="1">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="102" x14ac:dyDescent="0.2">
@@ -913,34 +925,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="1">
-        <v>3</v>
+      <c r="I7" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="102" x14ac:dyDescent="0.2">
@@ -948,34 +960,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="1">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="102" x14ac:dyDescent="0.2">
@@ -983,31 +995,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="1">
-        <v>2</v>
+        <v>44</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1015,31 +1027,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="1">
-        <v>5</v>
+      <c r="I10" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="119" x14ac:dyDescent="0.2">
@@ -1047,31 +1059,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="1">
-        <v>5</v>
+      <c r="I11" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Баг_Репорты ДЗ №2.xlsx
+++ b/Баг_Репорты ДЗ №2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivankosarev/Documents/ВУЗ/Программная инженерия/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7108E28E-99F7-7B42-A4DD-47A1B80FAC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6165C3-6174-1F43-886D-FE3E5C4BDC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17140" xr2:uid="{2F60AE98-D34A-7F44-8ACA-8D360F42C4F9}"/>
   </bookViews>
@@ -717,7 +717,7 @@
     <col min="6" max="6" width="19.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="19.33203125" customWidth="1"/>
     <col min="11" max="11" width="27.5" customWidth="1"/>
   </cols>
